--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008524561436371531</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>47845175</v>
+        <v>4045994</v>
       </c>
       <c r="L2" t="n">
-        <v>25279607</v>
+        <v>1634885</v>
       </c>
       <c r="M2" t="n">
-        <v>5774269</v>
+        <v>278042</v>
       </c>
       <c r="N2" t="n">
-        <v>235519</v>
+        <v>4641</v>
       </c>
       <c r="O2" t="n">
-        <v>3509662</v>
+        <v>174823</v>
       </c>
       <c r="P2" t="n">
-        <v>1253441</v>
+        <v>29208</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999842047691345</v>
+        <v>0.9999825954437256</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8327383399009705</v>
+        <v>0.7111683487892151</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7022417187690735</v>
+        <v>0.5328753590583801</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6330196857452393</v>
+        <v>0.3971132338047028</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2661547362804413</v>
+        <v>0.045680932700634</v>
       </c>
       <c r="V2" t="n">
-        <v>0.676479697227478</v>
+        <v>0.4257008731365204</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8174979686737061</v>
+        <v>0.6238093376159668</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00204248073217291</v>
       </c>
       <c r="C3" t="n">
-        <v>446</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>47845175</v>
+        <v>4045994</v>
       </c>
       <c r="E3" t="n">
-        <v>6965370</v>
+        <v>859938</v>
       </c>
       <c r="F3" t="n">
-        <v>181696</v>
+        <v>31766</v>
       </c>
       <c r="G3" t="n">
-        <v>13304</v>
+        <v>2583</v>
       </c>
       <c r="H3" t="n">
-        <v>13327</v>
+        <v>3590</v>
       </c>
       <c r="I3" t="n">
-        <v>378</v>
+        <v>71</v>
       </c>
       <c r="J3" t="n">
-        <v>110181744</v>
+        <v>10016512</v>
       </c>
       <c r="K3" t="n">
-        <v>114995847</v>
+        <v>9742417</v>
       </c>
       <c r="L3" t="n">
-        <v>132764930</v>
+        <v>11563926</v>
       </c>
       <c r="M3" t="n">
-        <v>165981776</v>
+        <v>14963728</v>
       </c>
       <c r="N3" t="n">
-        <v>177992700</v>
+        <v>16142685</v>
       </c>
       <c r="O3" t="n">
-        <v>172334203</v>
+        <v>15581249</v>
       </c>
       <c r="P3" t="n">
-        <v>177217231</v>
+        <v>16118054</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8696008324623108</v>
+        <v>0.8183717727661133</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6994555592536926</v>
+        <v>0.4905859529972076</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5608096122741699</v>
+        <v>0.2946121692657471</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2394644170999527</v>
+        <v>0.05158959701657295</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6252812743186951</v>
+        <v>0.3411160409450531</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5888721942901611</v>
+        <v>0.1506094932556152</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03218358813514684</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>8844615</v>
+        <v>1465108</v>
       </c>
       <c r="E4" t="n">
-        <v>25279607</v>
+        <v>1634885</v>
       </c>
       <c r="F4" t="n">
-        <v>1716554</v>
+        <v>181222</v>
       </c>
       <c r="G4" t="n">
-        <v>85643</v>
+        <v>15506</v>
       </c>
       <c r="H4" t="n">
-        <v>201843</v>
+        <v>34334</v>
       </c>
       <c r="I4" t="n">
-        <v>13547</v>
+        <v>1456</v>
       </c>
       <c r="J4" t="n">
-        <v>1098</v>
+        <v>110</v>
       </c>
       <c r="K4" t="n">
-        <v>9610057</v>
+        <v>1643227</v>
       </c>
       <c r="L4" t="n">
-        <v>10718835</v>
+        <v>1433159</v>
       </c>
       <c r="M4" t="n">
-        <v>3347515</v>
+        <v>422116</v>
       </c>
       <c r="N4" t="n">
-        <v>649376</v>
+        <v>96955</v>
       </c>
       <c r="O4" t="n">
-        <v>1678464</v>
+        <v>235848</v>
       </c>
       <c r="P4" t="n">
-        <v>279824</v>
+        <v>17614</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999920725822449</v>
+        <v>0.9999912977218628</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8507704734802246</v>
+        <v>0.7610132098197937</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7008458971977234</v>
+        <v>0.5108569860458374</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5947307944297791</v>
+        <v>0.3382683098316193</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2521051168441772</v>
+        <v>0.04845580458641052</v>
       </c>
       <c r="V4" t="n">
-        <v>0.649873673915863</v>
+        <v>0.3787433207035065</v>
       </c>
       <c r="W4" t="n">
-        <v>0.684601902961731</v>
+        <v>0.2426377087831497</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>547777</v>
+        <v>132107</v>
       </c>
       <c r="E5" t="n">
-        <v>3019902</v>
+        <v>423589</v>
       </c>
       <c r="F5" t="n">
-        <v>5774269</v>
+        <v>278042</v>
       </c>
       <c r="G5" t="n">
-        <v>204215</v>
+        <v>25243</v>
       </c>
       <c r="H5" t="n">
-        <v>690552</v>
+        <v>79384</v>
       </c>
       <c r="I5" t="n">
-        <v>59508</v>
+        <v>5371</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7174521</v>
+        <v>897962</v>
       </c>
       <c r="L5" t="n">
-        <v>10862228</v>
+        <v>1697630</v>
       </c>
       <c r="M5" t="n">
-        <v>4522040</v>
+        <v>665714</v>
       </c>
       <c r="N5" t="n">
-        <v>748005</v>
+        <v>85319</v>
       </c>
       <c r="O5" t="n">
-        <v>2103271</v>
+        <v>337680</v>
       </c>
       <c r="P5" t="n">
-        <v>875104</v>
+        <v>164724</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999938607215881</v>
+        <v>0.9999932646751404</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9065579771995544</v>
+        <v>0.8443814516067505</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8798552751541138</v>
+        <v>0.8082752227783203</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9561890959739685</v>
+        <v>0.9333829283714294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9922205805778503</v>
+        <v>0.9888378381729126</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9789465665817261</v>
+        <v>0.9648780226707458</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935703873634338</v>
+        <v>0.9888339042663574</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>163</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>161409</v>
+        <v>24469</v>
       </c>
       <c r="E6" t="n">
-        <v>227953</v>
+        <v>27866</v>
       </c>
       <c r="F6" t="n">
-        <v>249134</v>
+        <v>24034</v>
       </c>
       <c r="G6" t="n">
-        <v>235519</v>
+        <v>4641</v>
       </c>
       <c r="H6" t="n">
-        <v>100737</v>
+        <v>8384</v>
       </c>
       <c r="I6" t="n">
-        <v>8609</v>
+        <v>544</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>52946</v>
+        <v>19793</v>
       </c>
       <c r="E7" t="n">
-        <v>460098</v>
+        <v>108302</v>
       </c>
       <c r="F7" t="n">
-        <v>1090917</v>
+        <v>156802</v>
       </c>
       <c r="G7" t="n">
-        <v>301359</v>
+        <v>42596</v>
       </c>
       <c r="H7" t="n">
-        <v>3509662</v>
+        <v>174823</v>
       </c>
       <c r="I7" t="n">
-        <v>197782</v>
+        <v>10172</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>3310</v>
+        <v>1750</v>
       </c>
       <c r="E8" t="n">
-        <v>45512</v>
+        <v>13464</v>
       </c>
       <c r="F8" t="n">
-        <v>109214</v>
+        <v>28292</v>
       </c>
       <c r="G8" t="n">
-        <v>44855</v>
+        <v>11027</v>
       </c>
       <c r="H8" t="n">
-        <v>672005</v>
+        <v>110156</v>
       </c>
       <c r="I8" t="n">
-        <v>1253441</v>
+        <v>29208</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
